--- a/Module-2-Ms.Excel.xlsx
+++ b/Module-2-Ms.Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ACTE\12-Microsoft office-Omaan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3D6CC2-6755-4E64-8E21-FD229B8CE324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE45B36-D38D-434A-A456-DD74EF6CDBC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="759" firstSheet="1" activeTab="6" xr2:uid="{1BC85062-6884-4BC5-B2B2-E757DA34D19A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="759" firstSheet="5" activeTab="7" xr2:uid="{1BC85062-6884-4BC5-B2B2-E757DA34D19A}"/>
   </bookViews>
   <sheets>
     <sheet name="Spreadsheet Basics" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,19 @@
     <sheet name="Charts &amp; Graphs" sheetId="5" r:id="rId5"/>
     <sheet name="Power function" sheetId="6" r:id="rId6"/>
     <sheet name="Vlookup" sheetId="7" r:id="rId7"/>
+    <sheet name="HLOOKUP" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId10"/>
+    <sheet name="Pivot table" sheetId="9" r:id="rId11"/>
+    <sheet name="Conditional formatting" sheetId="12" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="7" r:id="rId14"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="266">
   <si>
     <t>Module 2: Ms.Excel</t>
   </si>
@@ -722,12 +730,318 @@
   <si>
     <t>Bugha</t>
   </si>
+  <si>
+    <t>VLOOKUP(E3,A2:B7,2,FALSE)</t>
+  </si>
+  <si>
+    <t>VLOOKUP(L7,H2:J9,3,FALSE)</t>
+  </si>
+  <si>
+    <t>VLOOKUP(O3,'D:\ACTE\5-Advance Excel with finding Fraud &amp; anomalies\[Advance Excel class sheets-1.xlsx]HLOOKUP'!A2:C7,2,0)</t>
+  </si>
+  <si>
+    <t>HLOOKUP</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>INTEL</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>DVD</t>
+  </si>
+  <si>
+    <t>HLOOKUP(B4,$F$6:$K$8,3,FALSE)</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Rate (Rs.)</t>
+  </si>
+  <si>
+    <t>Amount (Rs.)</t>
+  </si>
+  <si>
+    <t>Amit Sharma</t>
+  </si>
+  <si>
+    <t>Raj Verma</t>
+  </si>
+  <si>
+    <t>Neha Gupta</t>
+  </si>
+  <si>
+    <t>Laptop Stand</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>Headphones</t>
+  </si>
+  <si>
+    <t>Pooja Mehta</t>
+  </si>
+  <si>
+    <t>USB Hub</t>
+  </si>
+  <si>
+    <t>Sanjay Kumar</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Riya Patel</t>
+  </si>
+  <si>
+    <t>External Hard Drive</t>
+  </si>
+  <si>
+    <t>Mohit Joshi</t>
+  </si>
+  <si>
+    <t>Mouse Pad</t>
+  </si>
+  <si>
+    <t>Sunil Yadav</t>
+  </si>
+  <si>
+    <t>Webcam</t>
+  </si>
+  <si>
+    <t>Kiran Desai</t>
+  </si>
+  <si>
+    <t>Laptop Charger</t>
+  </si>
+  <si>
+    <t>Alok Tiwari</t>
+  </si>
+  <si>
+    <t>USB Cable</t>
+  </si>
+  <si>
+    <t>Sneha Reddy</t>
+  </si>
+  <si>
+    <t>Wireless Mouse</t>
+  </si>
+  <si>
+    <t>Deepak Rawat</t>
+  </si>
+  <si>
+    <t>Cooling Pad</t>
+  </si>
+  <si>
+    <t>Priya Malhotra</t>
+  </si>
+  <si>
+    <t>Gaming Keyboard</t>
+  </si>
+  <si>
+    <t>Ankit Sinha</t>
+  </si>
+  <si>
+    <t>RAM (8GB)</t>
+  </si>
+  <si>
+    <t>Rohit Bansal</t>
+  </si>
+  <si>
+    <t>Pen Drive (64GB)</t>
+  </si>
+  <si>
+    <t>Suman Rai</t>
+  </si>
+  <si>
+    <t>Power Bank</t>
+  </si>
+  <si>
+    <t>Gaurav Khanna</t>
+  </si>
+  <si>
+    <t>Laptop Bag</t>
+  </si>
+  <si>
+    <t>Snehal Kapoor</t>
+  </si>
+  <si>
+    <t>SSD (512GB)</t>
+  </si>
+  <si>
+    <t>Tarun Mehta</t>
+  </si>
+  <si>
+    <t>Kavita Chawla</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Nitin Saxena</t>
+  </si>
+  <si>
+    <t>Wireless Keyboard</t>
+  </si>
+  <si>
+    <t>Meena Dubey</t>
+  </si>
+  <si>
+    <t>USB Flash Drive</t>
+  </si>
+  <si>
+    <t>Arjun Pillai</t>
+  </si>
+  <si>
+    <t>HDMI Cable</t>
+  </si>
+  <si>
+    <t>Bhavesh Thakur</t>
+  </si>
+  <si>
+    <t>Laptop Skin</t>
+  </si>
+  <si>
+    <t>Preeti Kaur</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>Suresh Menon</t>
+  </si>
+  <si>
+    <t>Graphics Card (4GB)</t>
+  </si>
+  <si>
+    <t>Jyoti Sharma</t>
+  </si>
+  <si>
+    <t>Smartwatch</t>
+  </si>
+  <si>
+    <t>Karthik Reddy</t>
+  </si>
+  <si>
+    <t>Bluetooth Adapter</t>
+  </si>
+  <si>
+    <t>Varsha Jain</t>
+  </si>
+  <si>
+    <t>Cooling Fan</t>
+  </si>
+  <si>
+    <t>Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Gaming Mouse</t>
+  </si>
+  <si>
+    <t>Swati Agarwal</t>
+  </si>
+  <si>
+    <t>USB Type-C Cable</t>
+  </si>
+  <si>
+    <t>Aditya Kapoor</t>
+  </si>
+  <si>
+    <t>Docking Hub</t>
+  </si>
+  <si>
+    <t>Manish Pandey</t>
+  </si>
+  <si>
+    <t>Mechanical Keyboard</t>
+  </si>
+  <si>
+    <t>Sheetal Rao</t>
+  </si>
+  <si>
+    <t>Wireless Earbuds</t>
+  </si>
+  <si>
+    <t>Yashwant Sinha</t>
+  </si>
+  <si>
+    <t>External SSD (1TB)</t>
+  </si>
+  <si>
+    <t>Divya Kulkarni</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Harsh Chauhan</t>
+  </si>
+  <si>
+    <t>VR Headset</t>
+  </si>
+  <si>
+    <t>Pankaj Narang</t>
+  </si>
+  <si>
+    <t>Cooling Gel Pad</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Quantity</t>
+  </si>
+  <si>
+    <t>Sum of Amount (Rs.)</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>select data and go to insert click pivot table</t>
+  </si>
+  <si>
+    <t>Conditional Formatting</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Finding Duplicate value</t>
+  </si>
+  <si>
+    <t>COUNTIF($H$2:$H$15,H2)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,6 +1218,21 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1163,7 +1492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1289,11 +1618,148 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -2907,6 +3373,2190 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Module-2-Ms.Excel.xlsx]Sheet3!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Quantity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="22"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="23"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="24"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="25"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="26"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="27"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="28"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="29"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="30"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="31"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="32"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="33"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="34"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="35"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="36"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="37"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="38"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$4:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="39"/>
+                <c:pt idx="0">
+                  <c:v>Aditya Kapoor</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alok Tiwari</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Amit Sharma</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ankit Sinha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Arjun Pillai</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Bhavesh Thakur</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Deepak Rawat</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Divya Kulkarni</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Gaurav Khanna</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Harsh Chauhan</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jyoti Sharma</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Karthik Reddy</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Kavita Chawla</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Kiran Desai</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Manish Pandey</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Meena Dubey</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Mohit Joshi</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Neha Gupta</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Nitin Saxena</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Pankaj Narang</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Pooja Mehta</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Preeti Kaur</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Priya Malhotra</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Raj Verma</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ravi Shankar</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Riya Patel</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Rohit Bansal</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Sanjay Kumar</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Sheetal Rao</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Sneha Reddy</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Snehal Kapoor</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Suman Rai</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Sunil Yadav</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Suresh Menon</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Swati Agarwal</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Tarun Mehta</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Varsha Jain</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Vikram Singh</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Yashwant Sinha</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$4:$B$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="39"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-50C3-48C0-BA74-C05218BAB328}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Amount (Rs.)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="22"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="23"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="24"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="25"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="26"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="27"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="28"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="29"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="30"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="31"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="32"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="33"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="34"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="35"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="36"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="37"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="38"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="70000"/>
+                  <a:lumOff val="30000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$4:$A$43</c:f>
+              <c:strCache>
+                <c:ptCount val="39"/>
+                <c:pt idx="0">
+                  <c:v>Aditya Kapoor</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Alok Tiwari</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Amit Sharma</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ankit Sinha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Arjun Pillai</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Bhavesh Thakur</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Deepak Rawat</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Divya Kulkarni</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Gaurav Khanna</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Harsh Chauhan</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jyoti Sharma</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Karthik Reddy</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Kavita Chawla</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Kiran Desai</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Manish Pandey</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Meena Dubey</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Mohit Joshi</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Neha Gupta</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Nitin Saxena</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Pankaj Narang</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Pooja Mehta</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Preeti Kaur</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Priya Malhotra</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Raj Verma</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Ravi Shankar</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Riya Patel</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>Rohit Bansal</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>Sanjay Kumar</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Sheetal Rao</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Sneha Reddy</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>Snehal Kapoor</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>Suman Rai</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>Sunil Yadav</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>Suresh Menon</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>Swati Agarwal</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>Tarun Mehta</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>Varsha Jain</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>Vikram Singh</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>Yashwant Sinha</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$4:$C$43</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="39"/>
+                <c:pt idx="0">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-50C3-48C0-BA74-C05218BAB328}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3067,6 +5717,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -5078,6 +7768,525 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -5259,6 +8468,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12A6C6B7-2513-64AD-BAE9-6CFF42AC77B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -5280,14 +8530,14 @@
       <sheetName val="Nested VLOOKUP"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
       <sheetData sheetId="8">
         <row r="2">
           <cell r="A2" t="str">
@@ -5356,11 +8606,1156 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Amit Kamat" refreshedDate="46103.876918055554" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="39" xr:uid="{DF13737A-5A29-4D8D-A98B-0DB5E42B48AE}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E40" sheet="Pivot table"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Employee Name" numFmtId="0">
+      <sharedItems count="39">
+        <s v="Amit Sharma"/>
+        <s v="Raj Verma"/>
+        <s v="Neha Gupta"/>
+        <s v="Vikram Singh"/>
+        <s v="Pooja Mehta"/>
+        <s v="Sanjay Kumar"/>
+        <s v="Riya Patel"/>
+        <s v="Mohit Joshi"/>
+        <s v="Sunil Yadav"/>
+        <s v="Kiran Desai"/>
+        <s v="Alok Tiwari"/>
+        <s v="Sneha Reddy"/>
+        <s v="Deepak Rawat"/>
+        <s v="Priya Malhotra"/>
+        <s v="Ankit Sinha"/>
+        <s v="Rohit Bansal"/>
+        <s v="Suman Rai"/>
+        <s v="Gaurav Khanna"/>
+        <s v="Snehal Kapoor"/>
+        <s v="Tarun Mehta"/>
+        <s v="Kavita Chawla"/>
+        <s v="Nitin Saxena"/>
+        <s v="Meena Dubey"/>
+        <s v="Arjun Pillai"/>
+        <s v="Bhavesh Thakur"/>
+        <s v="Preeti Kaur"/>
+        <s v="Suresh Menon"/>
+        <s v="Jyoti Sharma"/>
+        <s v="Karthik Reddy"/>
+        <s v="Varsha Jain"/>
+        <s v="Ravi Shankar"/>
+        <s v="Swati Agarwal"/>
+        <s v="Aditya Kapoor"/>
+        <s v="Manish Pandey"/>
+        <s v="Sheetal Rao"/>
+        <s v="Yashwant Sinha"/>
+        <s v="Divya Kulkarni"/>
+        <s v="Harsh Chauhan"/>
+        <s v="Pankaj Narang"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Item" numFmtId="0">
+      <sharedItems count="39">
+        <s v="Keyboard"/>
+        <s v="Mouse"/>
+        <s v="Laptop Stand"/>
+        <s v="Headphones"/>
+        <s v="USB Hub"/>
+        <s v="Monitor"/>
+        <s v="External Hard Drive"/>
+        <s v="Mouse Pad"/>
+        <s v="Webcam"/>
+        <s v="Laptop Charger"/>
+        <s v="USB Cable"/>
+        <s v="Wireless Mouse"/>
+        <s v="Cooling Pad"/>
+        <s v="Gaming Keyboard"/>
+        <s v="RAM (8GB)"/>
+        <s v="Pen Drive (64GB)"/>
+        <s v="Power Bank"/>
+        <s v="Laptop Bag"/>
+        <s v="SSD (512GB)"/>
+        <s v="Printer"/>
+        <s v="Speaker"/>
+        <s v="Wireless Keyboard"/>
+        <s v="USB Flash Drive"/>
+        <s v="HDMI Cable"/>
+        <s v="Laptop Skin"/>
+        <s v="Docking Station"/>
+        <s v="Graphics Card (4GB)"/>
+        <s v="Smartwatch"/>
+        <s v="Bluetooth Adapter"/>
+        <s v="Cooling Fan"/>
+        <s v="Gaming Mouse"/>
+        <s v="USB Type-C Cable"/>
+        <s v="Docking Hub"/>
+        <s v="Mechanical Keyboard"/>
+        <s v="Wireless Earbuds"/>
+        <s v="External SSD (1TB)"/>
+        <s v="Ethernet Cable"/>
+        <s v="VR Headset"/>
+        <s v="Cooling Gel Pad"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+    <cacheField name="Rate (Rs.)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="300" maxValue="25000"/>
+    </cacheField>
+    <cacheField name="Amount (Rs.)" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="600" maxValue="45000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="39">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="1200"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="800"/>
+    <n v="800"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="1500"/>
+    <n v="1500"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="2500"/>
+    <n v="5000"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="1000"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="1"/>
+    <n v="12000"/>
+    <n v="12000"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="1"/>
+    <n v="4500"/>
+    <n v="4500"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="3"/>
+    <n v="300"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="1"/>
+    <n v="3200"/>
+    <n v="3200"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="1"/>
+    <n v="2500"/>
+    <n v="2500"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="2"/>
+    <n v="500"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="1"/>
+    <n v="1200"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="12"/>
+    <n v="1"/>
+    <n v="1800"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="13"/>
+    <n v="10"/>
+    <n v="4500"/>
+    <n v="45000"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="14"/>
+    <n v="1"/>
+    <n v="3500"/>
+    <n v="3500"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="15"/>
+    <n v="2"/>
+    <n v="900"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="16"/>
+    <n v="1"/>
+    <n v="3000"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="17"/>
+    <n v="1"/>
+    <n v="2000"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="18"/>
+    <n v="1"/>
+    <n v="6000"/>
+    <n v="6000"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="19"/>
+    <n v="1"/>
+    <n v="15000"/>
+    <n v="15000"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="20"/>
+    <n v="1"/>
+    <n v="3500"/>
+    <n v="3500"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="21"/>
+    <n v="1"/>
+    <n v="2200"/>
+    <n v="2200"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="22"/>
+    <n v="2"/>
+    <n v="750"/>
+    <n v="1500"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="23"/>
+    <n v="3"/>
+    <n v="400"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="24"/>
+    <n v="1"/>
+    <n v="600"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="25"/>
+    <n v="1"/>
+    <n v="7000"/>
+    <n v="7000"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="26"/>
+    <n v="1"/>
+    <n v="14000"/>
+    <n v="14000"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="27"/>
+    <n v="1"/>
+    <n v="8000"/>
+    <n v="8000"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="28"/>
+    <n v="2"/>
+    <n v="1200"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="29"/>
+    <n v="1"/>
+    <n v="1800"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="30"/>
+    <n v="1"/>
+    <n v="3000"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="31"/>
+    <n v="3"/>
+    <n v="600"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="32"/>
+    <n v="1"/>
+    <n v="5500"/>
+    <n v="5500"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="33"/>
+    <n v="1"/>
+    <n v="5000"/>
+    <n v="5000"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="34"/>
+    <n v="1"/>
+    <n v="4500"/>
+    <n v="4500"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="35"/>
+    <n v="1"/>
+    <n v="11000"/>
+    <n v="11000"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="36"/>
+    <n v="2"/>
+    <n v="700"/>
+    <n v="1400"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="37"/>
+    <n v="1"/>
+    <n v="25000"/>
+    <n v="25000"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="38"/>
+    <n v="1"/>
+    <n v="900"/>
+    <n v="900"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5FE09850-8FBE-4719-BEA3-465D634CEFF8}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:C43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="40">
+        <item x="32"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="12"/>
+        <item x="36"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="21"/>
+        <item x="38"/>
+        <item x="4"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="8"/>
+        <item x="26"/>
+        <item x="31"/>
+        <item x="19"/>
+        <item x="29"/>
+        <item x="3"/>
+        <item x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="40">
+        <item x="28"/>
+        <item x="29"/>
+        <item x="38"/>
+        <item x="12"/>
+        <item x="32"/>
+        <item x="25"/>
+        <item x="36"/>
+        <item x="6"/>
+        <item x="35"/>
+        <item x="13"/>
+        <item x="30"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="9"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="33"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="31"/>
+        <item x="37"/>
+        <item x="8"/>
+        <item x="34"/>
+        <item x="21"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="40">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sum of Quantity" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Amount (Rs.)" fld="4" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <chartFormats count="43">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="122" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="123">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="124">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="125">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="126">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="127">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="128">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="129">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="130">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="131">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="132">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="133">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="134">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="135">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="136">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="137">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="138">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="139">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="140">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="141">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="142">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="143">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="144">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="145">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="146">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="147">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="148">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="149">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="150">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="27"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="151">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="28"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="152">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="29"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="153">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="30"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="154">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="31"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="155">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="32"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="156">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="33"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="157">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="34"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="158">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="35"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="159">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="36"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="160">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="37"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="161">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="38"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="162" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5825,6 +10220,1000 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F99CCF-1F61-4778-A21F-DB5F32439DE4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7C1EDE-B59D-44A7-8424-19EFE3503736}">
+  <sheetPr>
+    <tabColor theme="5" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="28">
+        <v>2</v>
+      </c>
+      <c r="D2" s="28">
+        <v>1200</v>
+      </c>
+      <c r="E2" s="70">
+        <f>C2*D2</f>
+        <v>2400</v>
+      </c>
+      <c r="G2" s="75" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="28">
+        <v>1</v>
+      </c>
+      <c r="D3" s="28">
+        <v>800</v>
+      </c>
+      <c r="E3" s="70">
+        <f t="shared" ref="E3:E40" si="0">C3*D3</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="28">
+        <v>1</v>
+      </c>
+      <c r="D4" s="28">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="70">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="28">
+        <v>2</v>
+      </c>
+      <c r="D5" s="28">
+        <v>2500</v>
+      </c>
+      <c r="E5" s="70">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="28">
+        <v>1</v>
+      </c>
+      <c r="D6" s="28">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="70">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="28">
+        <v>1</v>
+      </c>
+      <c r="D7" s="28">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="70">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="28">
+        <v>1</v>
+      </c>
+      <c r="D8" s="28">
+        <v>4500</v>
+      </c>
+      <c r="E8" s="70">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="28">
+        <v>3</v>
+      </c>
+      <c r="D9" s="28">
+        <v>300</v>
+      </c>
+      <c r="E9" s="70">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="28">
+        <v>1</v>
+      </c>
+      <c r="D10" s="28">
+        <v>3200</v>
+      </c>
+      <c r="E10" s="70">
+        <f t="shared" si="0"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="28">
+        <v>1</v>
+      </c>
+      <c r="D11" s="28">
+        <v>2500</v>
+      </c>
+      <c r="E11" s="70">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="28">
+        <v>2</v>
+      </c>
+      <c r="D12" s="28">
+        <v>500</v>
+      </c>
+      <c r="E12" s="70">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="28">
+        <v>1</v>
+      </c>
+      <c r="D13" s="28">
+        <v>1200</v>
+      </c>
+      <c r="E13" s="70">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="28">
+        <v>1</v>
+      </c>
+      <c r="D14" s="28">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="70">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="28">
+        <v>10</v>
+      </c>
+      <c r="D15" s="28">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="70">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="28">
+        <v>1</v>
+      </c>
+      <c r="D16" s="28">
+        <v>3500</v>
+      </c>
+      <c r="E16" s="70">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="28">
+        <v>2</v>
+      </c>
+      <c r="D17" s="28">
+        <v>900</v>
+      </c>
+      <c r="E17" s="70">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="28">
+        <v>1</v>
+      </c>
+      <c r="D18" s="28">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="70">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="28">
+        <v>1</v>
+      </c>
+      <c r="D19" s="28">
+        <v>2000</v>
+      </c>
+      <c r="E19" s="70">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="28">
+        <v>1</v>
+      </c>
+      <c r="D20" s="28">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="70">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="28">
+        <v>1</v>
+      </c>
+      <c r="D21" s="28">
+        <v>15000</v>
+      </c>
+      <c r="E21" s="70">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="28">
+        <v>1</v>
+      </c>
+      <c r="D22" s="28">
+        <v>3500</v>
+      </c>
+      <c r="E22" s="70">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C23" s="28">
+        <v>1</v>
+      </c>
+      <c r="D23" s="28">
+        <v>2200</v>
+      </c>
+      <c r="E23" s="70">
+        <f t="shared" si="0"/>
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C24" s="28">
+        <v>2</v>
+      </c>
+      <c r="D24" s="28">
+        <v>750</v>
+      </c>
+      <c r="E24" s="70">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="28">
+        <v>3</v>
+      </c>
+      <c r="D25" s="28">
+        <v>400</v>
+      </c>
+      <c r="E25" s="70">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" s="28">
+        <v>1</v>
+      </c>
+      <c r="D26" s="28">
+        <v>600</v>
+      </c>
+      <c r="E26" s="70">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="28">
+        <v>1</v>
+      </c>
+      <c r="D27" s="28">
+        <v>7000</v>
+      </c>
+      <c r="E27" s="70">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="28">
+        <v>14000</v>
+      </c>
+      <c r="E28" s="70">
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29" s="28">
+        <v>1</v>
+      </c>
+      <c r="D29" s="28">
+        <v>8000</v>
+      </c>
+      <c r="E29" s="70">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="28">
+        <v>2</v>
+      </c>
+      <c r="D30" s="28">
+        <v>1200</v>
+      </c>
+      <c r="E30" s="70">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C31" s="28">
+        <v>1</v>
+      </c>
+      <c r="D31" s="28">
+        <v>1800</v>
+      </c>
+      <c r="E31" s="70">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="28">
+        <v>1</v>
+      </c>
+      <c r="D32" s="28">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="70">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C33" s="28">
+        <v>3</v>
+      </c>
+      <c r="D33" s="28">
+        <v>600</v>
+      </c>
+      <c r="E33" s="70">
+        <f t="shared" si="0"/>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" s="28">
+        <v>1</v>
+      </c>
+      <c r="D34" s="28">
+        <v>5500</v>
+      </c>
+      <c r="E34" s="70">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" s="28">
+        <v>1</v>
+      </c>
+      <c r="D35" s="28">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="70">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="28">
+        <v>1</v>
+      </c>
+      <c r="D36" s="28">
+        <v>4500</v>
+      </c>
+      <c r="E36" s="70">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" s="28">
+        <v>1</v>
+      </c>
+      <c r="D37" s="28">
+        <v>11000</v>
+      </c>
+      <c r="E37" s="70">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="28">
+        <v>2</v>
+      </c>
+      <c r="D38" s="28">
+        <v>700</v>
+      </c>
+      <c r="E38" s="70">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="C39" s="28">
+        <v>1</v>
+      </c>
+      <c r="D39" s="28">
+        <v>25000</v>
+      </c>
+      <c r="E39" s="70">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" s="28">
+        <v>1</v>
+      </c>
+      <c r="D40" s="28">
+        <v>900</v>
+      </c>
+      <c r="E40" s="70">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927988AB-5DC0-4175-99B2-FF3AEC15D38B}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1" s="45">
+        <v>10</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="I1" s="48" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>263</v>
+      </c>
+      <c r="F2" s="45">
+        <v>20</v>
+      </c>
+      <c r="H2" s="76">
+        <v>75</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF($H$2:$H$15,H2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="76">
+        <v>75</v>
+      </c>
+      <c r="F3" s="45">
+        <v>90</v>
+      </c>
+      <c r="H3" s="76">
+        <v>50</v>
+      </c>
+      <c r="I3">
+        <f>COUNTIF($H$2:$H$15,H3)</f>
+        <v>3</v>
+      </c>
+      <c r="J3" s="67" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="76">
+        <v>50</v>
+      </c>
+      <c r="F4" s="45">
+        <v>90</v>
+      </c>
+      <c r="H4" s="76">
+        <v>80</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I3:I15" si="0">COUNTIF($H$2:$H$15,H4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="76">
+        <v>80</v>
+      </c>
+      <c r="F5" s="45">
+        <v>200</v>
+      </c>
+      <c r="H5" s="76">
+        <v>70</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="76">
+        <v>70</v>
+      </c>
+      <c r="F6" s="45">
+        <v>50</v>
+      </c>
+      <c r="H6" s="76">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="76">
+        <v>50</v>
+      </c>
+      <c r="F7" s="45">
+        <v>20</v>
+      </c>
+      <c r="H7" s="76">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="76">
+        <v>50</v>
+      </c>
+      <c r="F8" s="45">
+        <v>100</v>
+      </c>
+      <c r="H8" s="76">
+        <v>60</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="76">
+        <v>60</v>
+      </c>
+      <c r="F9" s="45">
+        <v>101</v>
+      </c>
+      <c r="H9" s="76">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="76">
+        <v>30</v>
+      </c>
+      <c r="F10" s="45">
+        <v>60</v>
+      </c>
+      <c r="H10" s="76">
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="76">
+        <v>40</v>
+      </c>
+      <c r="H11" s="76">
+        <v>80</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="76">
+        <v>80</v>
+      </c>
+      <c r="H12" s="76">
+        <v>110</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="76">
+        <v>110</v>
+      </c>
+      <c r="H13" s="76">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="76">
+        <v>25</v>
+      </c>
+      <c r="H14" s="76">
+        <v>200</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="76">
+        <v>200</v>
+      </c>
+      <c r="H15" s="76">
+        <v>85</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="76">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A3:A16">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F10">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H15">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F421525F-3AFE-404C-A9E9-DDF6C8F3B64D}">
   <sheetPr>
@@ -7422,7 +12811,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="8.28515625" customWidth="1"/>
@@ -7439,12 +12828,12 @@
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="59" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
         <v>130</v>
       </c>
@@ -7482,7 +12871,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="45">
         <v>30</v>
       </c>
@@ -7533,8 +12922,11 @@
         <f>VLOOKUP(O3,[1]HLOOKUP!A2:C7,2,0)</f>
         <v>43842</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V3" s="67" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="45">
         <v>60</v>
       </c>
@@ -7588,7 +12980,7 @@
         <v>43529</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="45">
         <v>85</v>
       </c>
@@ -7628,7 +13020,7 @@
         <v>44395</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="45">
         <v>88</v>
       </c>
@@ -7674,7 +13066,7 @@
         <v>44096</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="45">
         <v>70</v>
       </c>
@@ -7721,7 +13113,7 @@
         <v>43414</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D8" s="60" t="s">
         <v>130</v>
       </c>
@@ -7748,7 +13140,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D9" s="60" t="s">
         <v>131</v>
       </c>
@@ -7776,7 +13168,10 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="67" t="s">
+        <v>164</v>
+      </c>
       <c r="L10" s="45" t="s">
         <v>162</v>
       </c>
@@ -7802,7 +13197,7 @@
       </c>
       <c r="T10" s="66"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="O11" s="65">
         <v>104</v>
       </c>
@@ -7821,7 +13216,10 @@
       </c>
       <c r="T11" s="66"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K12" s="67" t="s">
+        <v>165</v>
+      </c>
       <c r="O12" s="65">
         <v>101</v>
       </c>
@@ -7842,5 +13240,629 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B903E4-D81A-4361-86E2-3EC5400D7A8B}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.4">
+      <c r="A1" s="68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="45">
+        <v>111</v>
+      </c>
+      <c r="C4" s="45" t="str">
+        <f>HLOOKUP(B4,$F$6:$K$8,3,FALSE)</f>
+        <v>Laptop</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="45">
+        <v>222</v>
+      </c>
+      <c r="C5" s="45" t="str">
+        <f t="shared" ref="C5:C10" si="0">HLOOKUP(B5,$F$6:$K$8,3,FALSE)</f>
+        <v>Keyboard</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="45">
+        <v>333</v>
+      </c>
+      <c r="C6" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Mouse</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="45">
+        <v>111</v>
+      </c>
+      <c r="H6" s="45">
+        <v>222</v>
+      </c>
+      <c r="I6" s="45">
+        <v>333</v>
+      </c>
+      <c r="J6" s="45">
+        <v>777</v>
+      </c>
+      <c r="K6" s="45">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="45">
+        <v>111</v>
+      </c>
+      <c r="C7" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Laptop</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="45">
+        <v>222</v>
+      </c>
+      <c r="C8" s="45" t="str">
+        <f>HLOOKUP(B8,$F$6:$K$8,3,FALSE)</f>
+        <v>Keyboard</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="45">
+        <v>888</v>
+      </c>
+      <c r="C9" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Printer</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="45">
+        <v>777</v>
+      </c>
+      <c r="C10" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>DVD</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="67" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A262387A-B20C-412E-98C6-00A902ED2C60}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="73">
+        <v>1</v>
+      </c>
+      <c r="C4" s="74">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="73">
+        <v>2</v>
+      </c>
+      <c r="C5" s="74">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="73">
+        <v>2</v>
+      </c>
+      <c r="C6" s="74">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="73">
+        <v>1</v>
+      </c>
+      <c r="C7" s="74">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="73">
+        <v>3</v>
+      </c>
+      <c r="C8" s="74">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="73">
+        <v>1</v>
+      </c>
+      <c r="C9" s="74">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="73">
+        <v>1</v>
+      </c>
+      <c r="C10" s="74">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="72" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="73">
+        <v>2</v>
+      </c>
+      <c r="C11" s="74">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="72" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="73">
+        <v>1</v>
+      </c>
+      <c r="C12" s="74">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="73">
+        <v>1</v>
+      </c>
+      <c r="C13" s="74">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="73">
+        <v>1</v>
+      </c>
+      <c r="C14" s="74">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="72" t="s">
+        <v>234</v>
+      </c>
+      <c r="B15" s="73">
+        <v>2</v>
+      </c>
+      <c r="C15" s="74">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="73">
+        <v>1</v>
+      </c>
+      <c r="C16" s="74">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="B17" s="73">
+        <v>1</v>
+      </c>
+      <c r="C17" s="74">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="72" t="s">
+        <v>244</v>
+      </c>
+      <c r="B18" s="73">
+        <v>1</v>
+      </c>
+      <c r="C18" s="74">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="73">
+        <v>2</v>
+      </c>
+      <c r="C19" s="74">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="73">
+        <v>3</v>
+      </c>
+      <c r="C20" s="74">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="73">
+        <v>1</v>
+      </c>
+      <c r="C21" s="74">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="73">
+        <v>1</v>
+      </c>
+      <c r="C22" s="74">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="72" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" s="73">
+        <v>1</v>
+      </c>
+      <c r="C23" s="74">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="72" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="73">
+        <v>1</v>
+      </c>
+      <c r="C24" s="74">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="B25" s="73">
+        <v>1</v>
+      </c>
+      <c r="C25" s="74">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="73">
+        <v>10</v>
+      </c>
+      <c r="C26" s="74">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="73">
+        <v>1</v>
+      </c>
+      <c r="C27" s="74">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="72" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28" s="73">
+        <v>1</v>
+      </c>
+      <c r="C28" s="74">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="73">
+        <v>1</v>
+      </c>
+      <c r="C29" s="74">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="73">
+        <v>2</v>
+      </c>
+      <c r="C30" s="74">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="73">
+        <v>1</v>
+      </c>
+      <c r="C31" s="74">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="B32" s="73">
+        <v>1</v>
+      </c>
+      <c r="C32" s="74">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="73">
+        <v>1</v>
+      </c>
+      <c r="C33" s="74">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="73">
+        <v>1</v>
+      </c>
+      <c r="C34" s="74">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" s="73">
+        <v>1</v>
+      </c>
+      <c r="C35" s="74">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="73">
+        <v>1</v>
+      </c>
+      <c r="C36" s="74">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="B37" s="73">
+        <v>1</v>
+      </c>
+      <c r="C37" s="74">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="B38" s="73">
+        <v>3</v>
+      </c>
+      <c r="C38" s="74">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="72" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" s="73">
+        <v>1</v>
+      </c>
+      <c r="C39" s="74">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="72" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="73">
+        <v>1</v>
+      </c>
+      <c r="C40" s="74">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="73">
+        <v>2</v>
+      </c>
+      <c r="C41" s="74">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="72" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42" s="73">
+        <v>1</v>
+      </c>
+      <c r="C42" s="74">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="B43" s="73">
+        <v>61</v>
+      </c>
+      <c r="C43" s="74">
+        <v>214400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>